--- a/artfynd/A 43003-2024 artfynd.xlsx
+++ b/artfynd/A 43003-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72608880</v>
+        <v>72608879</v>
       </c>
       <c r="B2" t="n">
-        <v>81962</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111019</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>232272</v>
+        <v>222776</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcoscypha austriaca</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Beck) Boud.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Braxtorp - Nyckelbiotop, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>434142.5807708803</v>
+        <v>434085</v>
       </c>
       <c r="R2" t="n">
-        <v>6486432.217915931</v>
+        <v>6486362</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,19 +752,9 @@
           <t>2018-05-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-05-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -776,7 +768,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,52 +786,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>72608882</v>
+        <v>72608883</v>
       </c>
       <c r="B3" t="n">
-        <v>81962</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111019</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>232272</v>
+        <v>222776</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcoscypha austriaca</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Beck) Boud.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Braxtorp - Nyckelbiotop, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434134.9900521573</v>
+        <v>434164</v>
       </c>
       <c r="R3" t="n">
-        <v>6486478.848414243</v>
+        <v>6486443</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,19 +863,9 @@
           <t>2018-05-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-05-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -896,7 +879,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -915,59 +897,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>72608879</v>
+        <v>72608880</v>
       </c>
       <c r="B4" t="n">
-        <v>107845</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>84148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222776</v>
+        <v>232272</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Scharlakansskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Sarcoscypha austriaca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Beck) Boud.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Braxtorp - Nyckelbiotop, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434085.3892807081</v>
+        <v>434143</v>
       </c>
       <c r="R4" t="n">
-        <v>6486362.119204218</v>
+        <v>6486432</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,19 +967,9 @@
           <t>2018-05-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-05-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1023,6 +983,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1038,6 +999,111 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>72608882</v>
+      </c>
+      <c r="B5" t="n">
+        <v>84148</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>232272</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Scharlakansskål</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcoscypha austriaca</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Beck) Boud.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Braxtorp - Nyckelbiotop, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>434135</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6486479</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Frösve</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2018-05-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2018-05-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Alkärr och sumpskog</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
